--- a/GranBlueFantasy_And_OtherCygame_Support_Dll/package/LangMod/EN/CYgame_SourceCardEN.xlsx
+++ b/GranBlueFantasy_And_OtherCygame_Support_Dll/package/LangMod/EN/CYgame_SourceCardEN.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12525" tabRatio="500"/>
+    <workbookView windowWidth="27945" windowHeight="12525" tabRatio="500" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Element" sheetId="2" r:id="rId1"/>
@@ -6869,7 +6869,7 @@
     <t>domElement</t>
   </si>
   <si>
-    <t>CHA/15,END/15,cooking/10,anatomy/10,taming/20,counter/20,featRapidMagic/1,antiMagic/10,featGod_inui/1</t>
+    <t>CHA/15,END/15,cooking/10,anatomy/10,taming/20,counter/20,featRapidMagic/1,featGod_inui/1</t>
   </si>
   <si>
     <t>meat,egg,map</t>
